--- a/academias/Laboratorio Clínico - Estadisticos 20241.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20241.xlsx
@@ -1147,25 +1147,25 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1182,25 +1182,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>11.1</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1217,25 +1217,25 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>2.7</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1252,25 +1252,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>5.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1284,25 +1284,25 @@
         <v>146</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="F6">
-        <v>146</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>6.2</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J6">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1319,25 +1319,25 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1354,25 +1354,25 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>89.3</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>10.7</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1386,25 +1386,25 @@
         <v>53</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F9">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>86.8</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>13.2</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1421,25 +1421,25 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1456,25 +1456,25 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1488,25 +1488,25 @@
         <v>53</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F12">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>7.5</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1523,25 +1523,25 @@
         <v>41</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F13">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="J13">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1558,25 +1558,25 @@
         <v>41</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F14">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="J14">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1593,25 +1593,25 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1628,25 +1628,25 @@
         <v>36</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F16">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J16">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1660,25 +1660,25 @@
         <v>154</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="F17">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="J17">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1689,25 +1689,25 @@
         <v>406</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="F18">
-        <v>406</v>
+        <v>20</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J18">
-        <v>406</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1775,19 +1775,19 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>63.9</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>36.1</v>
+        <v>5.6</v>
       </c>
       <c r="I2" s="2">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1810,19 +1810,19 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>80.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>19.4</v>
+        <v>11.1</v>
       </c>
       <c r="I3" s="2">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1845,19 +1845,19 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>89.2</v>
+        <v>97.3</v>
       </c>
       <c r="H4" s="1">
-        <v>10.8</v>
+        <v>2.7</v>
       </c>
       <c r="I4" s="2">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1880,16 +1880,16 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>91.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="I5" s="2">
         <v>8.6</v>
@@ -1912,19 +1912,19 @@
         <v>146</v>
       </c>
       <c r="E6">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>81.5</v>
+        <v>93.8</v>
       </c>
       <c r="H6" s="1">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="I6" s="2">
-        <v>7.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         <v>16</v>
       </c>
       <c r="I7" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1994,7 +1994,7 @@
         <v>10.7</v>
       </c>
       <c r="I8" s="2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>13.2</v>
       </c>
       <c r="I9" s="2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>8</v>
       </c>
       <c r="I10" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2084,19 +2084,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>82.09999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>17.9</v>
+        <v>7.1</v>
       </c>
       <c r="I11" s="2">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2116,19 +2116,19 @@
         <v>53</v>
       </c>
       <c r="E12">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>86.8</v>
+        <v>92.5</v>
       </c>
       <c r="H12" s="1">
-        <v>13.2</v>
+        <v>7.5</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2317,19 +2317,19 @@
         <v>406</v>
       </c>
       <c r="E18">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="F18">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G18" s="1">
-        <v>89.90000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>10.1</v>
+        <v>4.9</v>
       </c>
       <c r="I18" s="2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20241.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20241.xlsx
@@ -2049,19 +2049,19 @@
         <v>25</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2084,19 +2084,19 @@
         <v>28</v>
       </c>
       <c r="E11">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>92.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>7.1</v>
+        <v>21.4</v>
       </c>
       <c r="I11" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2116,19 +2116,19 @@
         <v>53</v>
       </c>
       <c r="E12">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>92.5</v>
+        <v>88.7</v>
       </c>
       <c r="H12" s="1">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="I12" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2163,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2317,19 +2317,19 @@
         <v>406</v>
       </c>
       <c r="E18">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F18">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G18" s="1">
-        <v>95.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="H18" s="1">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I18" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J18">
         <v>0</v>

--- a/academias/Laboratorio Clínico - Estadisticos 20241.xlsx
+++ b/academias/Laboratorio Clínico - Estadisticos 20241.xlsx
@@ -1775,19 +1775,19 @@
         <v>36</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1810,19 +1810,19 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1845,16 +1845,16 @@
         <v>37</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>8.699999999999999</v>
@@ -1880,19 +1880,19 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1912,19 +1912,19 @@
         <v>146</v>
       </c>
       <c r="E6">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>93.8</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1947,19 +1947,19 @@
         <v>25</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>96</v>
+      </c>
+      <c r="H7" s="1">
         <v>4</v>
       </c>
-      <c r="G7" s="1">
-        <v>84</v>
-      </c>
-      <c r="H7" s="1">
-        <v>16</v>
-      </c>
       <c r="I7" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1982,16 +1982,16 @@
         <v>28</v>
       </c>
       <c r="E8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>89.3</v>
+        <v>85.7</v>
       </c>
       <c r="H8" s="1">
-        <v>10.7</v>
+        <v>14.3</v>
       </c>
       <c r="I8" s="2">
         <v>7.6</v>
@@ -2014,16 +2014,16 @@
         <v>53</v>
       </c>
       <c r="E9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>86.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>13.2</v>
+        <v>9.4</v>
       </c>
       <c r="I9" s="2">
         <v>7.4</v>
@@ -2317,19 +2317,19 @@
         <v>406</v>
       </c>
       <c r="E18">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F18">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G18" s="1">
-        <v>94.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="H18" s="1">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="I18" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
         <v>0</v>
